--- a/histograms/histogram_avg_d_valence_electrons.xlsx
+++ b/histograms/histogram_avg_d_valence_electrons.xlsx
@@ -445,7 +445,7 @@
         <v>0.1451785714285714</v>
       </c>
       <c r="B2" t="n">
-        <v>5832</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>0.3355357142857143</v>
       </c>
       <c r="B3" t="n">
-        <v>1813</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>0.5258928571428572</v>
       </c>
       <c r="B4" t="n">
-        <v>6063</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>0.7162500000000001</v>
       </c>
       <c r="B5" t="n">
-        <v>8102</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>0.9066071428571429</v>
       </c>
       <c r="B6" t="n">
-        <v>1856</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>1.096964285714286</v>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>1.287321428571429</v>
       </c>
       <c r="B8" t="n">
-        <v>204</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -509,7 +509,7 @@
         <v>1.668035714285714</v>
       </c>
       <c r="B10" t="n">
-        <v>178</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>1.858392857142857</v>
       </c>
       <c r="B11" t="n">
-        <v>134</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>2.04875</v>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>2.239107142857143</v>
       </c>
       <c r="B13" t="n">
-        <v>259</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>2.429464285714285</v>
       </c>
       <c r="B14" t="n">
-        <v>729</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>2.619821428571429</v>
       </c>
       <c r="B15" t="n">
-        <v>895</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -573,7 +573,7 @@
         <v>3.190892857142857</v>
       </c>
       <c r="B18" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -597,7 +597,7 @@
         <v>3.761964285714286</v>
       </c>
       <c r="B21" t="n">
-        <v>224</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
